--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A0ABF6-CBBD-4360-B3F9-67B3F94BF1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2244AF0-015E-43BE-A172-71FB8BAD4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29565" yWindow="3555" windowWidth="27180" windowHeight="15570" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-29655" yWindow="1755" windowWidth="27180" windowHeight="15570" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -392,10 +392,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>체리 열 근 주세요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2|3|4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -404,15 +400,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1010|509</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>resource/sound/fruit_store/10_1.mp3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>망고스틴 열두 개 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바나나 열 근 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010|510</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1135,7 +1135,7 @@
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -1161,7 +1161,7 @@
         <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
@@ -1178,13 +1178,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -1197,16 +1197,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
         <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" t="s">
-        <v>33</v>
       </c>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2244AF0-015E-43BE-A172-71FB8BAD4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315F6167-6C73-49B6-B300-01D1C31F401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29655" yWindow="1755" windowWidth="27180" windowHeight="15570" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-30105" yWindow="2625" windowWidth="27180" windowHeight="15570" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -55,10 +55,6 @@
   </si>
   <si>
     <t>alt_word_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>resource/sound/fruit_store/1_1.mp3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -400,10 +396,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>resource/sound/fruit_store/10_1.mp3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>망고스틴 열두 개 주세요</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -413,6 +405,263 @@
   </si>
   <si>
     <t>1010|510</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/苹果多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/芒果多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/苹果一斤多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/芒果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两斤多少钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/苹果一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>个多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/芒果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两个多少钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/我要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两斤草莓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/我要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两个西瓜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/sentense/我要十斤香蕉.mp3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/我要十二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>个山竹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -420,7 +669,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +761,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -918,7 +1174,7 @@
     <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.375" customWidth="1"/>
-    <col min="6" max="6" width="35.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.875" customWidth="1"/>
     <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="36.75" bestFit="1" customWidth="1"/>
@@ -948,7 +1204,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
@@ -972,13 +1228,13 @@
         <v>501</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
@@ -998,13 +1254,13 @@
         <v>504</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="4"/>
       <c r="M3" s="9"/>
@@ -1018,19 +1274,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
@@ -1044,22 +1300,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:15" ht="18">
+    <row r="6" spans="1:15" ht="18.75">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1067,19 +1323,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
@@ -1093,16 +1349,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
@@ -1132,13 +1388,13 @@
         <v>507</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
@@ -1152,16 +1408,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>28</v>
-      </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
@@ -1175,21 +1431,21 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" ht="18.75">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1197,16 +1453,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" t="s">
         <v>30</v>
       </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315F6167-6C73-49B6-B300-01D1C31F401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF75D008-23A5-46E0-BDF2-F30BD76F5881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30105" yWindow="2625" windowWidth="27180" windowHeight="15570" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="120">
   <si>
     <t>id</t>
   </si>
@@ -650,6 +650,1080 @@
         <charset val="128"/>
       </rPr>
       <t>个山竹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 회사원인가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 졸업생이예요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4001|20000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000|20002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>上班族</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="FangSong"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4001|20008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 학생인가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4002|20010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 선생님이신가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>너희는 한국인이니?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 직장인이 아닙니다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들은 중국인이에요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀는 요리사예요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그는 가수예요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4004|20003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4003|20004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4007|20006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你是学生吗</t>
+  </si>
+  <si>
+    <t>你们是韩国人吗</t>
+  </si>
+  <si>
+    <t>他是歌手</t>
+  </si>
+  <si>
+    <t>他们是中国人</t>
+  </si>
+  <si>
+    <t>她是厨师</t>
+  </si>
+  <si>
+    <t>0|0.1|2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不是上班族</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{我}{是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毕业</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4006|20005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000|3001|20000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>你是学生吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>您</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是老</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>师吗</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>您是老师吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>你们是韩国人吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>我是毕业生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>他是歌手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>他们是中国人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>她是厨师</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>我不是上班族</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>你是上班族</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 여기 있어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행은 저기에 있어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어디 가세요?</t>
+  </si>
+  <si>
+    <r>
+      <t>{我}{在}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>行}{在}{那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>去}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哪儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1|1.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3100|20103</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것은 개입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狗</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것은 개 두 마리입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001|2024</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这是两只狗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1|1.2|2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000|3002|20104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것은 제 고양이입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这是我的猫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这不是我的猫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것은 제 고양이가 아닙니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3001|4000|3002|20104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{那}{是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>牛肉}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것은 소고기입니다.</t>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那是牛肉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3101|20111</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것은 3근의 소고기입니다.</t>
+  </si>
+  <si>
+    <t>1007|2021</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那是好吃的牛肉。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것은 맛있는 양고기입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001|3002|20113</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것은 귀한 닭고기입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000|3002|20114</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1|1.1|1.2|2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那是三斤牛肉。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/sentense/那是三斤牛肉.mp3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/sentense/那是好吃的牛肉.mp3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{那}{是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的牛肉}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/那是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贵的牛肉</t>
     </r>
     <r>
       <rPr>
@@ -669,7 +1743,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -769,6 +1843,97 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="FangSong"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF57A64A"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -800,7 +1965,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -822,9 +1987,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -832,6 +1994,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -1167,13 +2335,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.375" customWidth="1"/>
+    <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.875" customWidth="1"/>
     <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
@@ -1185,31 +2353,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
@@ -1224,7 +2392,7 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>501</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1236,8 +2404,8 @@
       <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15">
@@ -1263,8 +2431,8 @@
         <v>17</v>
       </c>
       <c r="H3" s="4"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
     </row>
     <row r="4" spans="1:15" ht="18">
       <c r="A4">
@@ -1288,8 +2456,8 @@
       <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15">
@@ -1311,8 +2479,8 @@
       <c r="F5" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="18.75">
@@ -1337,8 +2505,8 @@
       <c r="G6" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15" ht="18">
@@ -1360,18 +2528,18 @@
       <c r="F7" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15">
@@ -1384,7 +2552,7 @@
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>507</v>
       </c>
       <c r="E10" t="s">
@@ -1396,8 +2564,8 @@
       <c r="G10" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15">
@@ -1410,7 +2578,7 @@
       <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E11" t="s">
@@ -1419,8 +2587,8 @@
       <c r="F11" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15">
@@ -1433,7 +2601,7 @@
       <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E12" t="s">
@@ -1442,8 +2610,8 @@
       <c r="F12" t="s">
         <v>41</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:15" ht="18.75">
       <c r="A13">
@@ -1455,7 +2623,7 @@
       <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E13" t="s">
@@ -1464,47 +2632,468 @@
       <c r="F13" t="s">
         <v>42</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:15">
       <c r="D14" s="5"/>
       <c r="E14" s="1"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-    </row>
-    <row r="17" spans="4:13">
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-    </row>
-    <row r="18" spans="4:13">
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-    </row>
-    <row r="19" spans="4:13">
-      <c r="D19" s="10"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-    </row>
-    <row r="20" spans="4:13">
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="G20" s="4"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-    </row>
-    <row r="21" spans="4:13">
-      <c r="F21" s="4"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="D19" s="9"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26">
+        <v>6</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" t="s">
+        <v>100</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" t="s">
+        <v>105</v>
+      </c>
+      <c r="G38" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>8</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>8</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>8</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" t="s">
+        <v>119</v>
+      </c>
+      <c r="G41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>10</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="18">
+      <c r="A56">
+        <v>11</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>12</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>83</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF75D008-23A5-46E0-BDF2-F30BD76F5881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F3DEDF-C80E-488E-B332-A81FE717FBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -169,10 +169,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>504|1001|2021</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>사과 한 근 얼마예요?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -205,33 +201,6 @@
   </si>
   <si>
     <r>
-      <t>501|100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>|2021</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>{芒果}{多少}{</t>
     </r>
     <r>
@@ -314,64 +283,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>501|100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>|2022</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>망고 두 근 얼마예요?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>504|100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>|2022</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>딸기 두 근 주세요</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -384,27 +299,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2022|505</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2|3|4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1012|2022|508</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>망고스틴 열두 개 주세요</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>바나나 열 근 주세요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1010|510</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1365,10 +1268,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3100|20103</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>이것은 개입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1638,21 +1537,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3101|20111</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>저것은 3근의 소고기입니다.</t>
-  </si>
-  <si>
     <t>1007|2021</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>那是好吃的牛肉。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>저것은 맛있는 양고기입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1661,10 +1549,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>저것은 귀한 닭고기입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>100000|3002|20114</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1673,18 +1557,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>那是三斤牛肉。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>resource/sound/sentense/那是三斤牛肉.mp3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>resource/sound/sentense/那是好吃的牛肉.mp3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>{那}{是}{</t>
     </r>
@@ -1712,6 +1584,30 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>저것은 비싼 닭고기입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것은 7근의 소고기입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/sentense/那是七斤牛肉.mp3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那是七斤牛肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/sentense/那是好吃的羊肉.mp3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那是好吃的羊肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>resource/sound/sentense/那是</t>
     </r>
@@ -1723,7 +1619,690 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>贵的牛肉</t>
+      <t>贵的鸡肉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{洗手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>在}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>里}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{喜茶}{在}{几}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화장실이 어디에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤이티는 몇 층에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하철역이 어디에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이탄이 어디에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이디라오는 몇 층에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>루이신 커피는 몇 층에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20501|100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>|2021</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20504|1001|2021</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20501|100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>|2022</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20504|100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>|2022</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022|20505</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010|20510</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012|2022|20508</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이탄은 이 방향인가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>外</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>滩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>这个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{方向}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>滩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{是}{那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{方向}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>滩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{是}{反}{方向}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20121|5103</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20117|5102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동방명주는 저 방향인가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20122|20126</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디즈니랜드는 반대 방향인가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/洗手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>间在哪里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铁站在哪里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>滩在哪里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/喜茶在几</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/海底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>捞在几楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/瑞幸咖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>啡在几楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>滩是这个方向吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东方明珠是那个方向吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>迪士尼乐园是反方向吗</t>
     </r>
     <r>
       <rPr>
@@ -1743,7 +2322,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1934,6 +2513,43 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF57A64A"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1965,7 +2581,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1998,6 +2614,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2335,14 +2957,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="6" max="6" width="50.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.875" customWidth="1"/>
     <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="36.75" bestFit="1" customWidth="1"/>
@@ -2393,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="9">
-        <v>501</v>
+        <v>20501</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -2419,16 +3041,16 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>504</v>
+        <v>20504</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4"/>
       <c r="M3" s="8"/>
@@ -2445,16 +3067,16 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
         <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
@@ -2471,13 +3093,13 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
@@ -2494,16 +3116,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -2520,13 +3142,13 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
@@ -2553,13 +3175,13 @@
         <v>4</v>
       </c>
       <c r="D10" s="9">
-        <v>507</v>
+        <v>20507</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -2576,16 +3198,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
@@ -2602,13 +3224,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
@@ -2621,16 +3243,16 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
@@ -2670,19 +3292,19 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
@@ -2695,19 +3317,19 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G21" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
@@ -2720,19 +3342,19 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>52</v>
-      </c>
       <c r="F22" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -2743,19 +3365,19 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -2766,19 +3388,19 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2789,19 +3411,19 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2812,19 +3434,19 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -2835,19 +3457,19 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" t="s">
         <v>58</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -2858,19 +3480,19 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18">
@@ -2880,20 +3502,20 @@
       <c r="B33">
         <v>1</v>
       </c>
-      <c r="C33" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" t="s">
-        <v>89</v>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>20103</v>
       </c>
       <c r="E33" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2904,16 +3526,16 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
         <v>87</v>
-      </c>
-      <c r="D34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E34" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" t="s">
-        <v>95</v>
       </c>
       <c r="G34" s="11"/>
     </row>
@@ -2925,16 +3547,16 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G35" s="6"/>
     </row>
@@ -2946,19 +3568,19 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2968,20 +3590,20 @@
       <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" t="s">
-        <v>106</v>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>20111</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F38" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2992,19 +3614,19 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E39" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39" t="s">
         <v>107</v>
-      </c>
-      <c r="F39" t="s">
-        <v>116</v>
-      </c>
-      <c r="G39" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3015,16 +3637,16 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F40" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G40" t="s">
         <v>109</v>
@@ -3038,61 +3660,259 @@
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>20115</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F44" t="s">
+        <v>135</v>
+      </c>
+      <c r="G44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>9</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>20116</v>
+      </c>
+      <c r="E45" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>9</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>20117</v>
+      </c>
+      <c r="E46" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="18.75">
+      <c r="A50">
+        <v>10</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>20118</v>
+      </c>
+      <c r="E50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" t="s">
         <v>112</v>
       </c>
-      <c r="F41" t="s">
-        <v>119</v>
-      </c>
-      <c r="G41" t="s">
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>10</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>20119</v>
+      </c>
+      <c r="E51" t="s">
+        <v>117</v>
+      </c>
+      <c r="F51" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>10</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>20120</v>
+      </c>
+      <c r="E52" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>10</v>
-      </c>
-      <c r="B53">
+      <c r="F52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>11</v>
+      </c>
+      <c r="B55">
         <v>1</v>
       </c>
-      <c r="E53" t="s">
-        <v>81</v>
-      </c>
-      <c r="G53" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="18">
+      <c r="C55" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" t="s">
+        <v>126</v>
+      </c>
+      <c r="F55" t="s">
+        <v>141</v>
+      </c>
+      <c r="G55" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="18.75">
       <c r="A56">
         <v>11</v>
       </c>
       <c r="B56">
+        <v>2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" t="s">
+        <v>142</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>11</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" t="s">
+        <v>143</v>
+      </c>
+      <c r="G57" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="G58" s="13"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>99</v>
+      </c>
+      <c r="B65">
         <v>1</v>
       </c>
-      <c r="E56" t="s">
-        <v>82</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>12</v>
-      </c>
-      <c r="B60">
+      <c r="E65" t="s">
+        <v>74</v>
+      </c>
+      <c r="G65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="18">
+      <c r="A68">
+        <v>100</v>
+      </c>
+      <c r="B68">
         <v>1</v>
       </c>
-      <c r="E60" t="s">
-        <v>83</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>86</v>
+      <c r="E68" t="s">
+        <v>75</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>101</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>76</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F3DEDF-C80E-488E-B332-A81FE717FBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C0FA2A-835D-4487-86C6-1DC0F9ED1EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-35220" yWindow="2175" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2055,22 +2055,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>20121|5103</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20117|5102</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>동방명주는 저 방향인가요?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>20122|20126</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>디즈니랜드는 반대 방향인가요?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2315,6 +2303,18 @@
       </rPr>
       <t>.mp3</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30117|5102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30121|5103</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30122|20126</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3692,7 +3692,7 @@
         <v>113</v>
       </c>
       <c r="F44" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G44" t="s">
         <v>111</v>
@@ -3715,7 +3715,7 @@
         <v>115</v>
       </c>
       <c r="F45" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>20117</v>
+        <v>30117</v>
       </c>
       <c r="E46" t="s">
         <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="18.75">
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>20118</v>
+        <v>30118</v>
       </c>
       <c r="E50" t="s">
         <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G50" t="s">
         <v>112</v>
@@ -3772,13 +3772,13 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>20119</v>
+        <v>30119</v>
       </c>
       <c r="E51" t="s">
         <v>117</v>
       </c>
       <c r="F51" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3792,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>20120</v>
+        <v>30120</v>
       </c>
       <c r="E52" t="s">
         <v>118</v>
       </c>
       <c r="F52" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3812,13 +3812,13 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E55" t="s">
         <v>126</v>
       </c>
       <c r="F55" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G55" t="s">
         <v>127</v>
@@ -3835,13 +3835,13 @@
         <v>38</v>
       </c>
       <c r="D56" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" t="s">
         <v>130</v>
       </c>
-      <c r="E56" t="s">
-        <v>132</v>
-      </c>
       <c r="F56" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>128</v>
@@ -3858,13 +3858,13 @@
         <v>38</v>
       </c>
       <c r="D57" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E57" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F57" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G57" t="s">
         <v>129</v>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C0FA2A-835D-4487-86C6-1DC0F9ED1EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCEAF5F-1F9A-4463-900C-D79E5E2AC981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35220" yWindow="2175" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="169">
   <si>
     <t>id</t>
   </si>
@@ -2315,6 +2315,304 @@
   </si>
   <si>
     <t>30122|20126</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 장원영 같은 헤어스타일로 자르고 싶어요</t>
+  </si>
+  <si>
+    <t>30134|5019</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想剪张元英那样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{我}{想}{剪}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张元英</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{的}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{我}{想}{剪}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这种</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>型}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 이런 스타일로 자르고 싶어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3|4|5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 한국 스타일로 자르고 싶어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20119|0|0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想剪韩式短发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>我想剪短</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3|4|5|6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20118|0|0|0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 단발 머리로 자르고 싶어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>有点}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1|2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>300000|100004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>300000|100006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물 온도가 조금 뜨거워요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물 온도가 조금 차가워요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40000|0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40001|0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물 온도가 너무 뜨거워요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물 온도가 너무 차가워요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|5019</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2957,13 +3255,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="5" max="5" width="43.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="50.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.875" customWidth="1"/>
     <col min="8" max="8" width="7.875" bestFit="1" customWidth="1"/>
@@ -3873,45 +4171,220 @@
     <row r="58" spans="1:7">
       <c r="G58" s="13"/>
     </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>12</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59" t="s">
+        <v>144</v>
+      </c>
+      <c r="F59" t="s">
+        <v>146</v>
+      </c>
+      <c r="G59" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>12</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" t="s">
+        <v>149</v>
+      </c>
+      <c r="F60" t="s">
+        <v>146</v>
+      </c>
+      <c r="G60" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>12</v>
+      </c>
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" t="s">
+        <v>152</v>
+      </c>
+      <c r="E61" t="s">
+        <v>151</v>
+      </c>
+      <c r="F61" t="s">
+        <v>146</v>
+      </c>
+      <c r="G61" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>12</v>
+      </c>
+      <c r="B62">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>155</v>
+      </c>
+      <c r="D62" t="s">
+        <v>156</v>
+      </c>
+      <c r="E62" t="s">
+        <v>157</v>
+      </c>
+      <c r="F62" t="s">
+        <v>146</v>
+      </c>
+      <c r="G62" t="s">
+        <v>154</v>
+      </c>
+    </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
+      <c r="C65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" t="s">
+        <v>160</v>
+      </c>
       <c r="E65" t="s">
+        <v>162</v>
+      </c>
+      <c r="F65" t="s">
+        <v>146</v>
+      </c>
+      <c r="G65" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>13</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" t="s">
+        <v>161</v>
+      </c>
+      <c r="E66" t="s">
+        <v>163</v>
+      </c>
+      <c r="F66" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>13</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" t="s">
+        <v>164</v>
+      </c>
+      <c r="E67" t="s">
+        <v>166</v>
+      </c>
+      <c r="F67" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>13</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" t="s">
+        <v>165</v>
+      </c>
+      <c r="E68" t="s">
+        <v>167</v>
+      </c>
+      <c r="F68" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76">
+        <v>99</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
         <v>74</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G76" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="18">
-      <c r="A68">
+    <row r="79" spans="1:7" ht="18">
+      <c r="A79">
         <v>100</v>
       </c>
-      <c r="B68">
+      <c r="B79">
         <v>1</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E79" t="s">
         <v>75</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G79" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
-      <c r="A72">
+    <row r="83" spans="1:7">
+      <c r="A83">
         <v>101</v>
       </c>
-      <c r="B72">
+      <c r="B83">
         <v>1</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E83" t="s">
         <v>76</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="G83" s="6" t="s">
         <v>79</v>
       </c>
     </row>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCEAF5F-1F9A-4463-900C-D79E5E2AC981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA13D09E-8FB5-4143-97EA-7C299A04B4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="169">
   <si>
     <t>id</t>
   </si>
@@ -3255,7 +3255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -4388,6 +4388,52 @@
         <v>79</v>
       </c>
     </row>
+    <row r="85" spans="1:7">
+      <c r="A85">
+        <v>998</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85" s="9">
+        <v>20501</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F85" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86">
+        <v>999</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86" s="9">
+        <v>20501</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F86" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA13D09E-8FB5-4143-97EA-7C299A04B4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5525973-9F4E-4C8F-864E-40E3D7CF6CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="12345" yWindow="2085" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2612,7 +2612,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0|5019</t>
+    <t>0|5018</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5525973-9F4E-4C8F-864E-40E3D7CF6CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9586AC52-0EBF-4FCA-9FA7-0A9DB810817E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12345" yWindow="2085" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="10800" yWindow="2685" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2584,10 +2584,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>300000|100006</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>물 온도가 조금 뜨거워요</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2613,6 +2609,10 @@
   </si>
   <si>
     <t>0|5018</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>300000|100007</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4205,7 +4205,7 @@
         <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E60" t="s">
         <v>149</v>
@@ -4277,7 +4277,7 @@
         <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
         <v>146</v>
@@ -4297,10 +4297,10 @@
         <v>159</v>
       </c>
       <c r="D66" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F66" t="s">
         <v>146</v>
@@ -4317,10 +4317,10 @@
         <v>159</v>
       </c>
       <c r="D67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F67" t="s">
         <v>146</v>
@@ -4337,10 +4337,10 @@
         <v>159</v>
       </c>
       <c r="D68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F68" t="s">
         <v>146</v>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9586AC52-0EBF-4FCA-9FA7-0A9DB810817E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D273B60E-75A4-4ED5-83D2-3ABE32D3EF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10800" yWindow="2685" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="176">
   <si>
     <t>id</t>
   </si>
@@ -2612,7 +2612,196 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>300000|100007</t>
+    <t>300000|100006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想剪这样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想剪韩式发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想剪短发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水温有点烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水温有点凉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水温太烫了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水温太冷了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4171,98 +4360,6 @@
     <row r="58" spans="1:7">
       <c r="G58" s="13"/>
     </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>12</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" t="s">
-        <v>145</v>
-      </c>
-      <c r="E59" t="s">
-        <v>144</v>
-      </c>
-      <c r="F59" t="s">
-        <v>146</v>
-      </c>
-      <c r="G59" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>12</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" t="s">
-        <v>167</v>
-      </c>
-      <c r="E60" t="s">
-        <v>149</v>
-      </c>
-      <c r="F60" t="s">
-        <v>146</v>
-      </c>
-      <c r="G60" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>12</v>
-      </c>
-      <c r="B61">
-        <v>3</v>
-      </c>
-      <c r="C61" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" t="s">
-        <v>152</v>
-      </c>
-      <c r="E61" t="s">
-        <v>151</v>
-      </c>
-      <c r="F61" t="s">
-        <v>146</v>
-      </c>
-      <c r="G61" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62">
-        <v>12</v>
-      </c>
-      <c r="B62">
-        <v>4</v>
-      </c>
-      <c r="C62" t="s">
-        <v>155</v>
-      </c>
-      <c r="D62" t="s">
-        <v>156</v>
-      </c>
-      <c r="E62" t="s">
-        <v>157</v>
-      </c>
-      <c r="F62" t="s">
-        <v>146</v>
-      </c>
-      <c r="G62" t="s">
-        <v>154</v>
-      </c>
-    </row>
     <row r="65" spans="1:7">
       <c r="A65">
         <v>13</v>
@@ -4280,7 +4377,7 @@
         <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="G65" t="s">
         <v>158</v>
@@ -4303,7 +4400,7 @@
         <v>162</v>
       </c>
       <c r="F66" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4323,7 +4420,7 @@
         <v>165</v>
       </c>
       <c r="F67" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4343,7 +4440,99 @@
         <v>166</v>
       </c>
       <c r="F68" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>14</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" t="s">
+        <v>145</v>
+      </c>
+      <c r="E70" t="s">
+        <v>144</v>
+      </c>
+      <c r="F70" t="s">
         <v>146</v>
+      </c>
+      <c r="G70" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>14</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" t="s">
+        <v>167</v>
+      </c>
+      <c r="E71" t="s">
+        <v>149</v>
+      </c>
+      <c r="F71" t="s">
+        <v>169</v>
+      </c>
+      <c r="G71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>14</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>150</v>
+      </c>
+      <c r="D72" t="s">
+        <v>152</v>
+      </c>
+      <c r="E72" t="s">
+        <v>151</v>
+      </c>
+      <c r="F72" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>14</v>
+      </c>
+      <c r="B73">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" t="s">
+        <v>157</v>
+      </c>
+      <c r="F73" t="s">
+        <v>171</v>
+      </c>
+      <c r="G73" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:7">

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D273B60E-75A4-4ED5-83D2-3ABE32D3EF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F869F44-5DC2-4260-A93B-EFC2418380B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="855" yWindow="2400" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2789,7 +2789,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>水温太冷了</t>
+      <t>水温太凉了</t>
     </r>
     <r>
       <rPr>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F869F44-5DC2-4260-A93B-EFC2418380B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CD37FC-C394-48C6-97FC-8A20B16F9889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="2400" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-32115" yWindow="2340" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="244">
   <si>
     <t>id</t>
   </si>
@@ -2803,13 +2803,1318 @@
       <t>.mp3</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{不}{要}{香菜}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不要香菜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고수 빼주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>쯔란 빼주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>식초 빼주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|1|2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|40002|20132</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>마늘 많이 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|40002|20133</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파 많이 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|40003|20129</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>마라 적게 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|40003|20134</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>务员</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>},{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{我}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{冰水}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20122</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>종업원님, 앞치마 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>종업원님, 얼음물 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20141</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20135</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>종업원님, 메뉴판 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기요, 포크 하나 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|3.1|3.2|4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40004|1003|2022|20142</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40004|1001|2022|20136</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40004|1000|2022|20137</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40004|1001|2027|20138</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20018|1000|2028|20152</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20018|1000|2026|20151</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 카드 결제 되나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{老板},{可以}{刷}{卡}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2|3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10014|20144</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 알리페이 결제 되나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 위쳇페이 결제 되나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10015|20145</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10015|20146</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고추기름 적게 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20018|1000|2025|20150</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|3.1|4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40004|40005|20140</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 사이다 한 캔 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 맥주 한 잔 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 콜라 한 병 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기요, 젓가락 두 쌍 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기요, 접시 세 개 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기요, 숟가락 두 개 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기요, 티슈 조금 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不要孜然</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不要醋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多放点蒜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多放点葱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>少放点麻辣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>少放点辣椒油</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>务员</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我冰水</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>务员</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>围</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>裙</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>务员</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我菜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>好,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>叉子</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>好,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>两</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>勺子</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>好,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我三</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>碟子</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>好,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>两</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>双</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>筷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>子</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>好,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>纸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>巾</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>老板,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>瓶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>乐</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>老板,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我一罐雪碧</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>老板,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>我一杯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>啤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>酒</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>老板,可以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>扫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>支付</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>宝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>老板,可以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>扫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>微信支付</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>老板,可以刷卡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>吗</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3036,6 +4341,13 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3444,7 +4756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -4537,89 +5849,521 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>20128</v>
+      </c>
       <c r="E76" t="s">
+        <v>178</v>
+      </c>
+      <c r="F76" t="s">
+        <v>177</v>
+      </c>
+      <c r="G76" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77">
+        <v>15</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>20130</v>
+      </c>
+      <c r="E77" t="s">
+        <v>179</v>
+      </c>
+      <c r="F77" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78">
+        <v>15</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>20131</v>
+      </c>
+      <c r="E78" t="s">
+        <v>180</v>
+      </c>
+      <c r="F78" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79">
+        <v>15</v>
+      </c>
+      <c r="B79">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>181</v>
+      </c>
+      <c r="D79" t="s">
+        <v>182</v>
+      </c>
+      <c r="E79" t="s">
+        <v>183</v>
+      </c>
+      <c r="F79" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80">
+        <v>15</v>
+      </c>
+      <c r="B80">
+        <v>5</v>
+      </c>
+      <c r="C80" t="s">
+        <v>181</v>
+      </c>
+      <c r="D80" t="s">
+        <v>184</v>
+      </c>
+      <c r="E80" t="s">
+        <v>185</v>
+      </c>
+      <c r="F80" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81">
+        <v>15</v>
+      </c>
+      <c r="B81">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>181</v>
+      </c>
+      <c r="D81" t="s">
+        <v>186</v>
+      </c>
+      <c r="E81" t="s">
+        <v>187</v>
+      </c>
+      <c r="F81" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>15</v>
+      </c>
+      <c r="B82">
+        <v>7</v>
+      </c>
+      <c r="C82" t="s">
+        <v>181</v>
+      </c>
+      <c r="D82" t="s">
+        <v>188</v>
+      </c>
+      <c r="E82" t="s">
+        <v>213</v>
+      </c>
+      <c r="F82" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="18">
+      <c r="A84">
+        <v>16</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>190</v>
+      </c>
+      <c r="D84" t="s">
+        <v>191</v>
+      </c>
+      <c r="E84" t="s">
+        <v>193</v>
+      </c>
+      <c r="F84" t="s">
+        <v>230</v>
+      </c>
+      <c r="G84" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="18">
+      <c r="A85">
+        <v>16</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85" t="s">
+        <v>190</v>
+      </c>
+      <c r="D85" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85" t="s">
+        <v>192</v>
+      </c>
+      <c r="F85" t="s">
+        <v>231</v>
+      </c>
+      <c r="G85" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="18">
+      <c r="A86">
+        <v>16</v>
+      </c>
+      <c r="B86">
+        <v>3</v>
+      </c>
+      <c r="C86" t="s">
+        <v>190</v>
+      </c>
+      <c r="D86" t="s">
+        <v>195</v>
+      </c>
+      <c r="E86" t="s">
+        <v>196</v>
+      </c>
+      <c r="F86" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87">
+        <v>16</v>
+      </c>
+      <c r="B87">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>198</v>
+      </c>
+      <c r="D87" t="s">
+        <v>201</v>
+      </c>
+      <c r="E87" t="s">
+        <v>197</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88">
+        <v>16</v>
+      </c>
+      <c r="B88">
+        <v>5</v>
+      </c>
+      <c r="C88" t="s">
+        <v>198</v>
+      </c>
+      <c r="D88" t="s">
+        <v>200</v>
+      </c>
+      <c r="E88" t="s">
+        <v>222</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>16</v>
+      </c>
+      <c r="B89">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D89" t="s">
+        <v>199</v>
+      </c>
+      <c r="E89" t="s">
+        <v>221</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>16</v>
+      </c>
+      <c r="B90">
+        <v>7</v>
+      </c>
+      <c r="C90" t="s">
+        <v>198</v>
+      </c>
+      <c r="D90" t="s">
+        <v>202</v>
+      </c>
+      <c r="E90" t="s">
+        <v>220</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>16</v>
+      </c>
+      <c r="B91">
+        <v>8</v>
+      </c>
+      <c r="C91" t="s">
+        <v>215</v>
+      </c>
+      <c r="D91" t="s">
+        <v>216</v>
+      </c>
+      <c r="E91" t="s">
+        <v>223</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>16</v>
+      </c>
+      <c r="B92">
+        <v>9</v>
+      </c>
+      <c r="C92" t="s">
+        <v>198</v>
+      </c>
+      <c r="D92" t="s">
+        <v>214</v>
+      </c>
+      <c r="E92" t="s">
+        <v>219</v>
+      </c>
+      <c r="F92" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>16</v>
+      </c>
+      <c r="B93">
+        <v>10</v>
+      </c>
+      <c r="C93" t="s">
+        <v>198</v>
+      </c>
+      <c r="D93" t="s">
+        <v>203</v>
+      </c>
+      <c r="E93" t="s">
+        <v>217</v>
+      </c>
+      <c r="F93" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>16</v>
+      </c>
+      <c r="B94">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>198</v>
+      </c>
+      <c r="D94" t="s">
+        <v>204</v>
+      </c>
+      <c r="E94" t="s">
+        <v>218</v>
+      </c>
+      <c r="F94" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
+        <v>17</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>207</v>
+      </c>
+      <c r="D96" t="s">
+        <v>208</v>
+      </c>
+      <c r="E96" t="s">
+        <v>205</v>
+      </c>
+      <c r="F96" t="s">
+        <v>243</v>
+      </c>
+      <c r="G96" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97">
+        <v>17</v>
+      </c>
+      <c r="B97">
+        <v>2</v>
+      </c>
+      <c r="C97" t="s">
+        <v>207</v>
+      </c>
+      <c r="D97" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" t="s">
+        <v>209</v>
+      </c>
+      <c r="F97" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
+        <v>17</v>
+      </c>
+      <c r="B98">
+        <v>3</v>
+      </c>
+      <c r="C98" t="s">
+        <v>207</v>
+      </c>
+      <c r="D98" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" t="s">
+        <v>210</v>
+      </c>
+      <c r="F98" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
         <v>74</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G100" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="18">
-      <c r="A79">
+    <row r="103" spans="1:7" ht="18">
+      <c r="A103">
         <v>100</v>
       </c>
-      <c r="B79">
+      <c r="B103">
         <v>1</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E103" t="s">
         <v>75</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G103" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
-      <c r="A83">
+    <row r="107" spans="1:7">
+      <c r="A107">
         <v>101</v>
       </c>
-      <c r="B83">
+      <c r="B107">
         <v>1</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E107" t="s">
         <v>76</v>
       </c>
-      <c r="G83" s="6" t="s">
+      <c r="G107" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
-      <c r="A85">
+    <row r="109" spans="1:7">
+      <c r="A109">
         <v>998</v>
       </c>
-      <c r="B85">
+      <c r="B109">
         <v>1</v>
       </c>
-      <c r="C85">
+      <c r="C109">
         <v>0</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D109" s="9">
         <v>20501</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="E109" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F109" t="s">
         <v>26</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G109" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
-      <c r="A86">
+    <row r="110" spans="1:7">
+      <c r="A110">
         <v>999</v>
       </c>
-      <c r="B86">
+      <c r="B110">
         <v>1</v>
       </c>
-      <c r="C86">
+      <c r="C110">
         <v>0</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D110" s="9">
         <v>20501</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F110" t="s">
         <v>26</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G110" t="s">
         <v>8</v>
       </c>
     </row>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CD37FC-C394-48C6-97FC-8A20B16F9889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFC7ACA-43D4-413D-A035-B67D0C6A1EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32115" yWindow="2340" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="11025" yWindow="2310" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2856,26 +2856,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>마늘 많이 넣어주세요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>0|40002|20133</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>파 많이 넣어주세요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>0|40003|20129</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>마라 적게 넣어주세요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>0|40003|20134</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3140,10 +3128,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>사장님, 위쳇페이 결제 되나요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>10015|20145</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3152,10 +3136,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>고추기름 적게 넣어주세요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>20018|1000|2025|20150</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4108,6 +4088,26 @@
       </rPr>
       <t>吗</t>
     </r>
+  </si>
+  <si>
+    <t>파 좀 더 많이 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>마늘 좀 더 많이 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>마라 좀 더 적게 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고추기름 좀 더 적게 넣어주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 위챗페이 결제 되나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5887,7 +5887,7 @@
         <v>179</v>
       </c>
       <c r="F77" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5907,7 +5907,7 @@
         <v>180</v>
       </c>
       <c r="F78" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5924,10 +5924,10 @@
         <v>182</v>
       </c>
       <c r="E79" t="s">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="F79" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5941,13 +5941,13 @@
         <v>181</v>
       </c>
       <c r="D80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E80" t="s">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="F80" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5961,13 +5961,13 @@
         <v>181</v>
       </c>
       <c r="D81" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E81" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -5981,13 +5981,13 @@
         <v>181</v>
       </c>
       <c r="D82" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E82" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="F82" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="18">
@@ -5998,19 +5998,19 @@
         <v>1</v>
       </c>
       <c r="C84" t="s">
+        <v>187</v>
+      </c>
+      <c r="D84" t="s">
+        <v>188</v>
+      </c>
+      <c r="E84" t="s">
         <v>190</v>
       </c>
-      <c r="D84" t="s">
-        <v>191</v>
-      </c>
-      <c r="E84" t="s">
-        <v>193</v>
-      </c>
       <c r="F84" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G84" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="18">
@@ -6021,19 +6021,19 @@
         <v>2</v>
       </c>
       <c r="C85" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E85" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F85" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G85" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="18">
@@ -6044,16 +6044,16 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D86" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E86" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F86" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6064,16 +6064,16 @@
         <v>4</v>
       </c>
       <c r="C87" t="s">
+        <v>195</v>
+      </c>
+      <c r="D87" t="s">
         <v>198</v>
       </c>
-      <c r="D87" t="s">
-        <v>201</v>
-      </c>
       <c r="E87" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6084,16 +6084,16 @@
         <v>5</v>
       </c>
       <c r="C88" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D88" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E88" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6104,16 +6104,16 @@
         <v>6</v>
       </c>
       <c r="C89" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D89" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E89" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6124,16 +6124,16 @@
         <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E90" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6144,16 +6144,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D91" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E91" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6164,16 +6164,16 @@
         <v>9</v>
       </c>
       <c r="C92" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D92" t="s">
+        <v>209</v>
+      </c>
+      <c r="E92" t="s">
         <v>214</v>
       </c>
-      <c r="E92" t="s">
-        <v>219</v>
-      </c>
       <c r="F92" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6184,16 +6184,16 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D93" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E93" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F93" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6204,16 +6204,16 @@
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D94" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E94" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F94" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6224,19 +6224,19 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E96" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F96" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G96" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6247,16 +6247,16 @@
         <v>2</v>
       </c>
       <c r="C97" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D97" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E97" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6267,16 +6267,16 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
+        <v>204</v>
+      </c>
+      <c r="D98" t="s">
         <v>207</v>
       </c>
-      <c r="D98" t="s">
-        <v>211</v>
-      </c>
       <c r="E98" t="s">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="F98" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="1:7">

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFC7ACA-43D4-413D-A035-B67D0C6A1EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66106998-949F-4511-84D1-EE71E11E0804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11025" yWindow="2310" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-35025" yWindow="1920" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -2295,7 +2295,11 @@
           <t>0|40002|20132</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>마늘 좀 더 많이 넣어주세요</t>
@@ -2328,7 +2332,11 @@
           <t>0|40002|20133</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>파 좀 더 많이 넣어주세요</t>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,7 +2444,11 @@
           <t>20017|20122</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>종업원님, 얼음물 주세요</t>
@@ -2477,7 +2481,11 @@
           <t>20017|20141</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>종업원님, 앞치마 주세요</t>
@@ -2675,7 +2683,11 @@
           <t>40004|40005|20140</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>저기요, 티슈 조금 주세요</t>
@@ -2774,7 +2786,11 @@
           <t>20018|1000|2026|20151</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>사장님, 맥주 한 잔 주세요</t>
@@ -2816,7 +2832,11 @@
           <t>10014|20144</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>사장님, 카드 결제 되나요?</t>
@@ -2849,7 +2869,11 @@
           <t>10015|20146</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>사장님, 알리페이 결제 되나요?</t>
@@ -2882,7 +2906,11 @@
           <t>10015|20145</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>사장님, 위챗페이 결제 되나요?</t>
@@ -3090,6 +3118,39 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2|3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>10016|20509</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>resource/sound/sentense/老板可以付现金吗.mp3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resource/table/sub_sentences.xlsx
+++ b/resource/table/sub_sentences.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3151,6 +3151,105 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>우리 택시타고 가자</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>resource/sound/sentense/我们打车去吧.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>20510</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>우리 택시타고 공항 가자</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>resource/sound/sentense/我们打车去机场吧.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>20511</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>우리 택시타고 호텔가자</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>resource/sound/sentense/我们打车去酒店吧.mp3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
